--- a/data/trans_orig/P33B_R5-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/P33B_R5-Habitat-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>41527</t>
+          <t>45782</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31041</t>
+          <t>34476</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>54013</t>
+          <t>58934</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,64%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,55%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>92177</t>
+          <t>102199</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>80668</t>
+          <t>89250</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>106972</t>
+          <t>118918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,65%</t>
+          <t>13,95%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,94%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,84%</t>
+          <t>16,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>133703</t>
+          <t>147981</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>118231</t>
+          <t>128998</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>151931</t>
+          <t>167138</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,21%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,75%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>592885</t>
+          <t>643846</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>580399</t>
+          <t>630694</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>603371</t>
+          <t>655152</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,36%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,49%</t>
+          <t>91,45%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>95,11%</t>
+          <t>95,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>583193</t>
+          <t>630523</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>568398</t>
+          <t>613804</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>594702</t>
+          <t>643472</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,35%</t>
+          <t>86,05%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,16%</t>
+          <t>83,77%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>88,06%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>1176079</t>
+          <t>1274369</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1157851</t>
+          <t>1255212</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1191551</t>
+          <t>1293352</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>89,79%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>90,97%</t>
+          <t>90,93%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>634412</t>
+          <t>689628</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -986,17 +986,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>675370</t>
+          <t>732722</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>1309782</t>
+          <t>1422350</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1068,32 +1068,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>55109</t>
+          <t>61337</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27848</t>
+          <t>48606</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77880</t>
+          <t>78795</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1103,32 +1103,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>121751</t>
+          <t>135870</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105903</t>
+          <t>119521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>138150</t>
+          <t>153945</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>12,71%</t>
+          <t>12,69%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,05%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1138,32 +1138,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>176860</t>
+          <t>197207</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>116171</t>
+          <t>172972</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208513</t>
+          <t>221385</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>8,22%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>9,69%</t>
+          <t>10,44%</t>
         </is>
       </c>
     </row>
@@ -1181,32 +1181,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1137755</t>
+          <t>987580</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1114984</t>
+          <t>970122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1165016</t>
+          <t>1000311</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>95,38%</t>
+          <t>94,15%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>92,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1216,32 +1216,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>836355</t>
+          <t>934968</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>819956</t>
+          <t>916893</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>852203</t>
+          <t>951317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>85,58%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1974111</t>
+          <t>1922548</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1942458</t>
+          <t>1898370</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2034800</t>
+          <t>1946783</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>91,78%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>90,31%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>94,6%</t>
+          <t>91,84%</t>
         </is>
       </c>
     </row>
@@ -1294,17 +1294,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1192864</t>
+          <t>1048917</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1329,17 +1329,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>958106</t>
+          <t>1070838</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1364,17 +1364,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2150971</t>
+          <t>2119755</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1411,32 +1411,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>43046</t>
+          <t>47448</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>31989</t>
+          <t>35200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>56047</t>
+          <t>61705</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,39%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1446,32 +1446,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>80106</t>
+          <t>92374</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>76849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>110865</t>
+          <t>111342</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>11,39%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,08%</t>
+          <t>9,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>11,89%</t>
+          <t>13,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1481,32 +1481,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>123152</t>
+          <t>139822</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>80576</t>
+          <t>120643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>151181</t>
+          <t>164273</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>7,48%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -1524,32 +1524,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>660638</t>
+          <t>754638</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>647637</t>
+          <t>740381</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>671695</t>
+          <t>766886</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>94,08%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>92,04%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,61%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1559,32 +1559,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>852104</t>
+          <t>718620</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>821345</t>
+          <t>699652</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>894155</t>
+          <t>734145</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>88,61%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>88,11%</t>
+          <t>86,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1594,32 +1594,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1512742</t>
+          <t>1473257</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1484713</t>
+          <t>1448806</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1555318</t>
+          <t>1492436</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>91,33%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>90,76%</t>
+          <t>89,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>92,52%</t>
         </is>
       </c>
     </row>
@@ -1637,17 +1637,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>703684</t>
+          <t>802086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1672,17 +1672,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>932210</t>
+          <t>810994</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1707,17 +1707,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>1635894</t>
+          <t>1613079</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1754,32 +1754,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79235</t>
+          <t>83010</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64793</t>
+          <t>68887</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96178</t>
+          <t>103934</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,38%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,32 +1789,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>133597</t>
+          <t>143792</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108743</t>
+          <t>126853</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>158509</t>
+          <t>164628</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,86%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>9,95%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>14,51%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,32 +1824,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>212832</t>
+          <t>226802</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>181355</t>
+          <t>204512</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>240433</t>
+          <t>254188</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>8,98%</t>
+          <t>9,7%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,91%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -1867,32 +1867,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>847596</t>
+          <t>907052</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>830653</t>
+          <t>886128</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>862038</t>
+          <t>921175</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>91,45%</t>
+          <t>91,62%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,62%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>93,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,32 +1902,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>958996</t>
+          <t>974527</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>934084</t>
+          <t>953691</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>983850</t>
+          <t>991466</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>87,77%</t>
+          <t>87,14%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>85,49%</t>
+          <t>85,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>90,05%</t>
+          <t>88,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,32 +1937,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1806592</t>
+          <t>1881579</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1778991</t>
+          <t>1854193</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1838069</t>
+          <t>1903869</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,24%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,09%</t>
+          <t>87,94%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>91,02%</t>
+          <t>90,3%</t>
         </is>
       </c>
     </row>
@@ -1980,17 +1980,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>926831</t>
+          <t>990062</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2015,17 +2015,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>1092593</t>
+          <t>1118319</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2050,17 +2050,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>2019424</t>
+          <t>2108381</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2097,32 +2097,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>218916</t>
+          <t>237576</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>168381</t>
+          <t>208439</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>253439</t>
+          <t>268293</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>5,9%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,33%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2132,32 +2132,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>427630</t>
+          <t>474236</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>348865</t>
+          <t>441591</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>472318</t>
+          <t>507802</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>9,54%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>13,6%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2167,32 +2167,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>646547</t>
+          <t>711812</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>557091</t>
+          <t>668340</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>705134</t>
+          <t>756581</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>9,8%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,42%</t>
         </is>
       </c>
     </row>
@@ -2210,32 +2210,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>3238875</t>
+          <t>3293117</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3204352</t>
+          <t>3262400</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>3289410</t>
+          <t>3322254</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,67%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>95,13%</t>
+          <t>94,1%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,32 +2245,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>3230649</t>
+          <t>3258637</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>3185961</t>
+          <t>3225071</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>3309414</t>
+          <t>3291282</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>88,31%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>87,09%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>90,46%</t>
+          <t>88,17%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,32 +2280,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>6469523</t>
+          <t>6551753</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>6410936</t>
+          <t>6506984</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>6558979</t>
+          <t>6595225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,2%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>90,09%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>90,8%</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>3457791</t>
+          <t>3530693</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2358,17 +2358,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>3658279</t>
+          <t>3732873</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2393,17 +2393,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>7116070</t>
+          <t>7263565</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
